--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="481">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -753,7 +753,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1994: source value from AR TRANSACTION - TRANSACTION NUMBER (433-.01)</t>
+    <t>1994: source value based on AR TRANSACTION - TRANSACTION NUMBER (433-.01)</t>
   </si>
   <si>
     <t>IB.ARTransaction.TransactionNumber</t>
@@ -860,7 +860,7 @@
     <t>ChargeItem.identifier:va-bn.value</t>
   </si>
   <si>
-    <t>1995: source value from AR TRANSACTION - BILL NUMBER (433-.03)</t>
+    <t>1995: source value based on AR TRANSACTION - BILL NUMBER (433-.03)</t>
   </si>
   <si>
     <t>IB.ARTransaction.AccountsReceivableIEN,IB.ARTransaction.PatientIEN,IB.ARTransactionComment.PatientIEN,IB.ARTransactionDescription.PatientIEN,IB.ARTransactionFiscalYear.PatientIEN</t>
@@ -1009,7 +1009,11 @@
     <t>ChargeItem.code.text</t>
   </si>
   <si>
-    <t>1993: source value from AR TRANSACTION - TRANSACTION TYPE &gt; ACCOUNTS RECEIVABLE TRANS.TYPE - NAME (433-12 &gt; 430.3-.01) case IEN = 12 OR 13</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpci-28-1993:If IEN = 12 OR 13 then source value from (433-12 &gt; 430.3-.01) {null}</t>
+  </si>
+  <si>
+    <t>1993: source value based on AR TRANSACTION - TRANSACTION TYPE &gt; ACCOUNTS RECEIVABLE TRANS.TYPE - NAME (433-12 &gt; 430.3-.01) if IEN = 12 OR 13</t>
   </si>
   <si>
     <t>IB.ARTransaction.ARTransactionTypeIEN
@@ -1123,7 +1127,7 @@
 </t>
   </si>
   <si>
-    <t>1997: source value from AR TRANSACTION - TRANSACTION DATE (433-11)</t>
+    <t>1997: source value based on AR TRANSACTION - TRANSACTION DATE (433-11)</t>
   </si>
   <si>
     <t>IB.ARTransaction.TransactionDateTime,IB.ARTransactionComment.TransactionDateTime,IB.ARTransactionDescription.TransactionDateTime,IB.ARTransactionFiscalYear.TransactionDateTime</t>
@@ -1377,7 +1381,7 @@
     <t>The actual date when the service associated with the charge has been rendered is captured in occurrence[x].</t>
   </si>
   <si>
-    <t>1998: source value from AR TRANSACTION - DATE ENTERED (433-19)</t>
+    <t>1998: source value based on AR TRANSACTION - DATE ENTERED (433-19)</t>
   </si>
   <si>
     <t>IB.ARTransaction.EnteredDateTime</t>
@@ -1860,7 +1864,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="144.1875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="145.21875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="175.2265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
@@ -7379,13 +7383,13 @@
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>321</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7402,14 +7406,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7428,17 +7432,17 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7487,7 +7491,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>90</v>
@@ -7508,28 +7512,28 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7548,17 +7552,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7607,7 +7611,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7628,28 +7632,28 @@
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7668,16 +7672,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7715,7 +7719,7 @@
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -7725,7 +7729,7 @@
         <v>153</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7746,30 +7750,30 @@
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>281</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7788,16 +7792,16 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7847,7 +7851,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7862,30 +7866,30 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>281</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7908,13 +7912,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7965,7 +7969,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7986,13 +7990,13 @@
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>79</v>
@@ -8000,10 +8004,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8118,10 +8122,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8238,14 +8242,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8267,10 +8271,10 @@
         <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>139</v>
@@ -8325,7 +8329,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8360,10 +8364,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8389,10 +8393,10 @@
         <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8422,10 +8426,10 @@
         <v>310</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8443,7 +8447,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8464,13 +8468,13 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>281</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>79</v>
@@ -8478,10 +8482,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8504,13 +8508,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8561,7 +8565,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>90</v>
@@ -8582,24 +8586,24 @@
         <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8625,13 +8629,13 @@
         <v>252</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8681,7 +8685,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8702,13 +8706,13 @@
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -8716,10 +8720,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8745,13 +8749,13 @@
         <v>252</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8801,7 +8805,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8828,7 +8832,7 @@
         <v>133</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>79</v>
@@ -8836,10 +8840,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8865,13 +8869,13 @@
         <v>252</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8921,7 +8925,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8945,7 +8949,7 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -8956,10 +8960,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8982,16 +8986,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9041,7 +9045,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9065,7 +9069,7 @@
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9076,10 +9080,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9105,13 +9109,13 @@
         <v>186</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9140,10 +9144,10 @@
         <v>310</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>79</v>
@@ -9161,7 +9165,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9188,7 +9192,7 @@
         <v>79</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>79</v>
@@ -9196,10 +9200,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9222,16 +9226,16 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9281,7 +9285,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9305,7 +9309,7 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9316,10 +9320,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9342,16 +9346,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9401,7 +9405,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9425,7 +9429,7 @@
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9436,10 +9440,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9465,13 +9469,13 @@
         <v>162</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9521,7 +9525,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9556,10 +9560,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9582,16 +9586,16 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9641,7 +9645,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9665,21 +9669,21 @@
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9702,16 +9706,16 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9761,7 +9765,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9776,10 +9780,10 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
@@ -9796,10 +9800,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9825,13 +9829,13 @@
         <v>186</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9860,10 +9864,10 @@
         <v>310</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -9881,7 +9885,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9902,24 +9906,24 @@
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9942,13 +9946,13 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9999,7 +10003,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10020,24 +10024,24 @@
         <v>79</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10060,13 +10064,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10096,10 +10100,10 @@
         <v>310</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -10117,7 +10121,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10144,7 +10148,7 @@
         <v>79</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>79</v>
@@ -10152,10 +10156,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10178,16 +10182,16 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10237,7 +10241,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10272,10 +10276,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10298,13 +10302,13 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10355,7 +10359,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10376,13 +10380,13 @@
         <v>79</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>79</v>
@@ -10390,10 +10394,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10416,13 +10420,13 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10473,7 +10477,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10494,7 +10498,7 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1010,7 +1010,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpci-28-1993:If IEN = 12 OR 13 then source value from (433-12 &gt; 430.3-.01) {null}</t>
+dpci-28-1993:If IEN = 12 OR 13 then source value from (433-12 &gt; 430.3-.01) {true}</t>
   </si>
   <si>
     <t>1993: source value based on AR TRANSACTION - TRANSACTION TYPE &gt; ACCOUNTS RECEIVABLE TRANS.TYPE - NAME (433-12 &gt; 430.3-.01) if IEN = 12 OR 13</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1381,7 +1381,7 @@
     <t>The actual date when the service associated with the charge has been rendered is captured in occurrence[x].</t>
   </si>
   <si>
-    <t>1998: source value based on AR TRANSACTION - DATE ENTERED (433-19)</t>
+    <t>1992: source value based on AR TRANSACTION - DATE ENTERED (433-19)</t>
   </si>
   <si>
     <t>IB.ARTransaction.EnteredDateTime</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeIteminterest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
